--- a/docs/revised_shatin/qwen3-235b-a22b-thinking-2507/test_grammar_4_['No. 63_～なら〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-235b-a22b-thinking-2507/test_grammar_4_['No. 63_～なら〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 雨が降る (   )、出かけるのをやめましょう。</t>
+          <t>: もんだい1 雨が降る (   )、出かけるのをやめましょう。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 時間がある (   )、一緒に映画を見に行きませんか。</t>
+          <t>: もんだい1 時間がある (   )、一緒に映画を見に行きませんか。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 明日が休み (   )、遊びに行こうよ。</t>
+          <t>: もんだい1 明日が休み (   )、遊びに行こうよ。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 この本を読む (   )、もっと日本の歴史がわかります。</t>
+          <t>: もんだい1 この本を読む (   )、もっと日本の歴史がわかります。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 彼が来る (   )、パーティーを始めましょう。</t>
+          <t>: もんだい1 彼が来る (   )、パーティーを始めましょう。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 日本語を勉強する (   )、毎日練習しなければなりません。</t>
+          <t>: もんだい1 日本語を勉強する (   )、毎日練習しなければなりません。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 行きたくない (   )、無理に行く必要はありません。</t>
+          <t>: もんだい1 行きたくない (   )、無理に行く必要はありません。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 天気がいい (   )、ピクニックに行きましょう。</t>
+          <t>: もんだい1 天気がいい (   )、ピクニックに行きましょう。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 お金が足りない (   )、買い物を控えよう。</t>
+          <t>: もんだい1 お金が足りない (   )、買い物を控えよう。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨がふる　(   )、かさを　もって　いきます。</t>
+          <t>: もんだい2 雨がふる　(   )、かさを　もって　いきます。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -702,12 +702,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が　ある　(   )、一緒に　映画を　見に　行きませんか。</t>
+          <t>: もんだい2 時間が　ある　(   )、一緒に　映画を　見に　行きませんか。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -726,12 +726,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 日本に　行く　(   )、お土産を　買って　きます。</t>
+          <t>: もんだい2 日本に　行く　(   )、お土産を　買って　きます。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -750,12 +750,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お茶が　好き　(   )、この店の　お茶を　飲んで　みて。</t>
+          <t>: もんだい2 お茶が　好き　(   )、この店の　お茶を　飲んで　みて。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -774,12 +774,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 明日　雨が　降る　(   )、ピクニックは　中止です。</t>
+          <t>: もんだい2 明日　雨が　降る　(   )、ピクニックは　中止です。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 この本を　読む　(   )、辞書が　必要です。</t>
+          <t>: もんだい2 この本を　読む　(   )、辞書が　必要です。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が　かかる　(   )、タクシーを　使いましょう。</t>
+          <t>: もんだい2 時間が　かかる　(   )、タクシーを　使いましょう。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -846,12 +846,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 旅行に　行く　(   )、パスポートを　忘れないで。</t>
+          <t>: もんだい2 旅行に　行く　(   )、パスポートを　忘れないで。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 彼が　来る　(   )、パーティーを　始めましょう。</t>
+          <t>: もんだい2 彼が　来る　(   )、パーティーを　始めましょう。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -894,12 +894,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金が　足りない　(   )、友達に　借りよう。</t>
+          <t>: もんだい2 お金が　足りない　(   )、友達に　借りよう。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -918,12 +918,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金がないなら、もっと(   )。</t>
+          <t>: もんだい3 お金がないなら、もっと(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -942,12 +942,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降るなら、(   )。</t>
+          <t>: もんだい3 雨が降るなら、(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -966,12 +966,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 暇(ひま)なら、映画を(   )。</t>
+          <t>: もんだい3 暇(ひま)なら、映画を(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 彼女が来るなら、(   )。</t>
+          <t>: もんだい3 彼女が来るなら、(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 安いなら、この服を(   )。</t>
+          <t>: もんだい3 安いなら、この服を(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1038,12 +1038,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があるなら、(   )。</t>
+          <t>: もんだい3 時間があるなら、(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1062,12 +1062,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 日本に行くなら、(   )。</t>
+          <t>: もんだい3 日本に行くなら、(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 彼が忙しいなら、(   )。</t>
+          <t>: もんだい3 彼が忙しいなら、(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1110,12 +1110,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 試験があるなら、(   )。</t>
+          <t>: もんだい3 試験があるなら、(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1134,12 +1134,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 部屋が寒いなら、(   )。</t>
+          <t>: もんだい3 部屋が寒いなら、(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1158,12 +1158,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし　明日　雨が　降るなら、　わたしは　家に　(   ).</t>
+          <t>: もんだい4 もし　明日　雨が　降るなら、　わたしは　家に　(   ).</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1182,12 +1182,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 映画館で　いい映画が　やっているなら、　みんなで　(   ).</t>
+          <t>: もんだい4 映画館で　いい映画が　やっているなら、　みんなで　(   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1206,12 +1206,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼が　パーティーに　来るなら、　私も　(   ).</t>
+          <t>: もんだい4 彼が　パーティーに　来るなら、　私も　(   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1230,12 +1230,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし　日本料理が　好きなら、　このレストランを　(   ).</t>
+          <t>: もんだい4 もし　日本料理が　好きなら、　このレストランを　(   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1254,12 +1254,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし　時間が　あるなら、　一緒に　(   ).</t>
+          <t>: もんだい4 もし　時間が　あるなら、　一緒に　(   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1278,12 +1278,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 新しいカフェが　オープンするなら、　週末に　(   ).</t>
+          <t>: もんだい4 新しいカフェが　オープンするなら、　週末に　(   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1302,12 +1302,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし　彼女が　その本を　読んでいるなら、　私も　(   ).</t>
+          <t>: もんだい4 もし　彼女が　その本を　読んでいるなら、　私も　(   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1326,12 +1326,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 お金が　たくさん　あるなら、　世界旅行を　(   ).</t>
+          <t>: もんだい4 お金が　たくさん　あるなら、　世界旅行を　(   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1350,12 +1350,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし　彼が　行くなら、　私も　(   )。</t>
+          <t>: もんだい4 もし　彼が　行くなら、　私も　(   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1374,12 +1374,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼女が　料理を　作るなら、　私も　手伝おうと　(   ).</t>
+          <t>: もんだい4 彼女が　料理を　作るなら、　私も　手伝おうと　(   ).</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 このりんごが安いなら、(   )。</t>
+          <t>: もんだい5 このりんごが安いなら、(   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1422,12 +1422,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が来るなら、(   )。</t>
+          <t>: もんだい5 彼が来るなら、(   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降るなら、(   )。</t>
+          <t>: もんだい5 雨が降るなら、(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1470,12 +1470,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 カレーを作るなら、(   )。</t>
+          <t>: もんだい5 カレーを作るなら、(   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1494,12 +1494,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼女が好きなら、(   )。</t>
+          <t>: もんだい5 彼女が好きなら、(   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 試験が難しいなら、(   )。</t>
+          <t>: もんだい5 試験が難しいなら、(   )。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1542,12 +1542,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 旅行に行くなら、(   )。</t>
+          <t>: もんだい5 旅行に行くなら、(   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1566,12 +1566,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この映画が面白いなら、(   )。</t>
+          <t>: もんだい5 この映画が面白いなら、(   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1590,12 +1590,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が先生なら、(   )。</t>
+          <t>: もんだい5 彼が先生なら、(   )。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 日本に住むなら、(   )。</t>
+          <t>: もんだい5 日本に住むなら、(   )。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「このレストランは美味しいですか。 」 B:「はい、美味しいですよ。 もし行く(   )、予約をしたほうがいいですよ。 」</t>
+          <t>: もんだい6 A:「このレストランは美味しいですか。 」 B:「はい、美味しいですよ。 もし行く(   )、予約をしたほうがいいですよ。 」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「田中さん、映画を見に行きませんか。 」 B:「映画ですか。 時間がある(   )、ぜひ行きたいです。 」</t>
+          <t>: もんだい6 A:「田中さん、映画を見に行きませんか。 」 B:「映画ですか。 時間がある(   )、ぜひ行きたいです。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1686,12 +1686,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、かぜをひいた(   )、この薬を飲んでください。 」 B:「はい、わかりました。 」</t>
+          <t>: もんだい6 A:「もし、かぜをひいた(   )、この薬を飲んでください。 」 B:「はい、わかりました。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1710,12 +1710,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「スキーが好きですか。 」 B:「はい、好きです。 でも、雪がたくさん降る(   )、行きたくないです。 」</t>
+          <t>: もんだい6 A:「スキーが好きですか。 」 B:「はい、好きです。 でも、雪がたくさん降る(   )、行きたくないです。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この本を読みたいですか。 」 B:「読みたいですが、面白くない(   )、読みません。 」</t>
+          <t>: もんだい6 A:「この本を読みたいですか。 」 B:「読みたいですが、面白くない(   )、読みません。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1758,12 +1758,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「旅行に行きたいですね。 」 B:「そうですね。 もし、お金がたくさんある(   )、ヨーロッパに行きたいです。 」</t>
+          <t>: もんだい6 A:「旅行に行きたいですね。 」 B:「そうですね。 もし、お金がたくさんある(   )、ヨーロッパに行きたいです。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1782,12 +1782,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「明日、雨が降る(   )、ピクニックは中止しましょう。 」 B:「そうですね、準備が必要ですね。 」</t>
+          <t>: もんだい6 A:「明日、雨が降る(   )、ピクニックは中止しましょう。 」 B:「そうですね、準備が必要ですね。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1806,12 +1806,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この問題が難しいですか。 」 B:「はい、難しいです。 でも、先生に聞く(   )、わかると思います。 」</t>
+          <t>: もんだい6 A:「この問題が難しいですか。 」 B:「はい、難しいです。 でも、先生に聞く(   )、わかると思います。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1830,12 +1830,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「しゅくだいを手伝ってくれませんか。 」 B:「いいですよ。 私でよければ、手伝う(   )。 」</t>
+          <t>: もんだい6 A:「しゅくだいを手伝ってくれませんか。 」 B:「いいですよ。 私でよければ、手伝う(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1854,12 +1854,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「新しいパソコンが欲しいですね。 」 B:「ええ、もし安く買える(   )、すぐに買いたいです。 」</t>
+          <t>: もんだい6 A:「新しいパソコンが欲しいですね。 」 B:「ええ、もし安く買える(   )、すぐに買いたいです。 」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 映画を見るなら、(   )。</t>
+          <t>: もんだい7 映画を見るなら、(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1902,12 +1902,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 雨が降るなら、(   )。</t>
+          <t>: もんだい7 雨が降るなら、(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1926,12 +1926,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 日本語を勉強するなら、(   )。</t>
+          <t>: もんだい7 日本語を勉強するなら、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 行かないなら、(   )。</t>
+          <t>: もんだい7 行かないなら、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1974,12 +1974,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼が来るなら、(   )。</t>
+          <t>: もんだい7 彼が来るなら、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -1998,12 +1998,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼女が行かないなら、(   )。</t>
+          <t>: もんだい7 彼女が行かないなら、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 勉強しないなら、(   )。</t>
+          <t>: もんだい7 勉強しないなら、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2046,12 +2046,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 行くなら、(   )。</t>
+          <t>: もんだい7 行くなら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼が手伝うなら、(   )。</t>
+          <t>: もんだい7 彼が手伝うなら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2094,12 +2094,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 日本に行くなら、(   )。</t>
+          <t>: もんだい7 日本に行くなら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2118,12 +2118,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし　天気 (てんき) が　いい (   )、公園 (こうえん) に　行きましょう。</t>
+          <t>: もんだい8 もし　天気 (てんき) が　いい (   )、公園 (こうえん) に　行きましょう。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2142,12 +2142,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 その　本 (ほん) を　読んだ (   )、感想 (かんそう) を　教えてください。</t>
+          <t>: もんだい8 その　本 (ほん) を　読んだ (   )、感想 (かんそう) を　教えてください。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2166,12 +2166,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 時間 (じかん) が　ある (   )、手伝って (てつだって) もらえますか。</t>
+          <t>: もんだい8 時間 (じかん) が　ある (   )、手伝って (てつだって) もらえますか。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2190,12 +2190,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 カメラを　使う (つかう) (   )、説明書 (せつめいしょ) を　読んでください。</t>
+          <t>: もんだい8 カメラを　使う (つかう) (   )、説明書 (せつめいしょ) を　読んでください。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし　雨 (あめ) が　降らない (   )、試合 (しあい) は　外 (そと) で　行います。</t>
+          <t>: もんだい8 もし　雨 (あめ) が　降らない (   )、試合 (しあい) は　外 (そと) で　行います。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この　映画 (えいが) を　見る (   )、泣いて (ないて) しまうかも。</t>
+          <t>: もんだい8 この　映画 (えいが) を　見る (   )、泣いて (ないて) しまうかも。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2262,12 +2262,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし　時間 (じかん) が　ない (   )、無理 (むり) しないでください。</t>
+          <t>: もんだい8 もし　時間 (じかん) が　ない (   )、無理 (むり) しないでください。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2286,12 +2286,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 英語 (えいご) が　上手 (じょうず) なら (   )、通訳 (つうやく) になれます。</t>
+          <t>: もんだい8 英語 (えいご) が　上手 (じょうず) なら (   )、通訳 (つうやく) になれます。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 その　問題 (もんだい) が　解決 (かいけつ) できる (   )、すぐに　連絡 (れんらく) します。</t>
+          <t>: もんだい8 その　問題 (もんだい) が　解決 (かいけつ) できる (   )、すぐに　連絡 (れんらく) します。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2334,12 +2334,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼 (かれ) が　来る (   )、パーティーを　始めましょう。</t>
+          <t>: もんだい8 彼 (かれ) が　来る (   )、パーティーを　始めましょう。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
